--- a/testdata/sample_employee_details_T001.xlsx
+++ b/testdata/sample_employee_details_T001.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AWSJ46</v>
+        <v>AVPX32</v>
       </c>
       <c r="B2" t="str">
-        <v>Ashlynn</v>
+        <v>Donnell</v>
       </c>
       <c r="C2" t="str">
-        <v>Wolff</v>
+        <v>Hickle</v>
       </c>
       <c r="D2" t="str">
         <v>Male</v>
@@ -481,7 +481,7 @@
         <v>9909909909</v>
       </c>
       <c r="F2" t="str">
-        <v>Douglas.Kunde17@gmail.com</v>
+        <v>Olive_Hagenes56@gmail.com</v>
       </c>
       <c r="G2" t="str">
         <v>1990-05-16</v>

--- a/testdata/sample_employee_details_T001.xlsx
+++ b/testdata/sample_employee_details_T001.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AVPX32</v>
+        <v>AIAR77</v>
       </c>
       <c r="B2" t="str">
-        <v>Donnell</v>
+        <v>Jordyn</v>
       </c>
       <c r="C2" t="str">
-        <v>Hickle</v>
+        <v>Ward</v>
       </c>
       <c r="D2" t="str">
         <v>Male</v>
@@ -481,7 +481,7 @@
         <v>9909909909</v>
       </c>
       <c r="F2" t="str">
-        <v>Olive_Hagenes56@gmail.com</v>
+        <v>Josh_MacGyver@gmail.com</v>
       </c>
       <c r="G2" t="str">
         <v>1990-05-16</v>

--- a/testdata/sample_employee_details_T001.xlsx
+++ b/testdata/sample_employee_details_T001.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AIAR77</v>
+        <v>AZIQ10</v>
       </c>
       <c r="B2" t="str">
-        <v>Jordyn</v>
+        <v>Rudolph</v>
       </c>
       <c r="C2" t="str">
-        <v>Ward</v>
+        <v>Mills</v>
       </c>
       <c r="D2" t="str">
         <v>Male</v>
@@ -481,7 +481,7 @@
         <v>9909909909</v>
       </c>
       <c r="F2" t="str">
-        <v>Josh_MacGyver@gmail.com</v>
+        <v>Raquel.Purdy@yahoo.com</v>
       </c>
       <c r="G2" t="str">
         <v>1990-05-16</v>

--- a/testdata/sample_employee_details_T001.xlsx
+++ b/testdata/sample_employee_details_T001.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AZIQ10</v>
+        <v>ANSZ18</v>
       </c>
       <c r="B2" t="str">
-        <v>Rudolph</v>
+        <v>Seth</v>
       </c>
       <c r="C2" t="str">
-        <v>Mills</v>
+        <v>Yost</v>
       </c>
       <c r="D2" t="str">
         <v>Male</v>
@@ -481,7 +481,7 @@
         <v>9909909909</v>
       </c>
       <c r="F2" t="str">
-        <v>Raquel.Purdy@yahoo.com</v>
+        <v>Eileen_Langosh85@hotmail.com</v>
       </c>
       <c r="G2" t="str">
         <v>1990-05-16</v>

--- a/testdata/sample_employee_details_T001.xlsx
+++ b/testdata/sample_employee_details_T001.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ANSZ18</v>
+        <v>AEEP76</v>
       </c>
       <c r="B2" t="str">
-        <v>Seth</v>
+        <v>Morris</v>
       </c>
       <c r="C2" t="str">
-        <v>Yost</v>
+        <v>OKeefe</v>
       </c>
       <c r="D2" t="str">
         <v>Male</v>
@@ -481,7 +481,7 @@
         <v>9909909909</v>
       </c>
       <c r="F2" t="str">
-        <v>Eileen_Langosh85@hotmail.com</v>
+        <v>Jeramy.Nicolas@hotmail.com</v>
       </c>
       <c r="G2" t="str">
         <v>1990-05-16</v>

--- a/testdata/sample_employee_details_T001.xlsx
+++ b/testdata/sample_employee_details_T001.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AEUA50</v>
+        <v>ADDC31</v>
       </c>
       <c r="B2" t="str">
-        <v>Amparo</v>
+        <v>Jasmine</v>
       </c>
       <c r="C2" t="str">
-        <v>Hilll</v>
+        <v>Lakin</v>
       </c>
       <c r="D2" t="str">
         <v>Male</v>
@@ -481,7 +481,7 @@
         <v>9909909909</v>
       </c>
       <c r="F2" t="str">
-        <v>Darnell71@gmail.com</v>
+        <v>Peter.Tillman78@hotmail.com</v>
       </c>
       <c r="G2" t="str">
         <v>1990-05-16</v>

--- a/testdata/sample_employee_details_T001.xlsx
+++ b/testdata/sample_employee_details_T001.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ADDC31</v>
+        <v>AFKA84</v>
       </c>
       <c r="B2" t="str">
-        <v>Jasmine</v>
+        <v>Jermaine</v>
       </c>
       <c r="C2" t="str">
-        <v>Lakin</v>
+        <v>Lubowitz</v>
       </c>
       <c r="D2" t="str">
         <v>Male</v>
@@ -481,7 +481,7 @@
         <v>9909909909</v>
       </c>
       <c r="F2" t="str">
-        <v>Peter.Tillman78@hotmail.com</v>
+        <v>Adam.Franey83@gmail.com</v>
       </c>
       <c r="G2" t="str">
         <v>1990-05-16</v>

--- a/testdata/sample_employee_details_T001.xlsx
+++ b/testdata/sample_employee_details_T001.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AFKA84</v>
+        <v>AUHU26</v>
       </c>
       <c r="B2" t="str">
-        <v>Jermaine</v>
+        <v>Pearl</v>
       </c>
       <c r="C2" t="str">
-        <v>Lubowitz</v>
+        <v>KrisKihn</v>
       </c>
       <c r="D2" t="str">
         <v>Male</v>
@@ -481,7 +481,7 @@
         <v>9909909909</v>
       </c>
       <c r="F2" t="str">
-        <v>Adam.Franey83@gmail.com</v>
+        <v>Emmy86@hotmail.com</v>
       </c>
       <c r="G2" t="str">
         <v>1990-05-16</v>

--- a/testdata/sample_employee_details_T001.xlsx
+++ b/testdata/sample_employee_details_T001.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AUHU26</v>
+        <v>AUIN37</v>
       </c>
       <c r="B2" t="str">
-        <v>Pearl</v>
+        <v>Johnpaul</v>
       </c>
       <c r="C2" t="str">
-        <v>KrisKihn</v>
+        <v>Blanda</v>
       </c>
       <c r="D2" t="str">
         <v>Male</v>
@@ -481,7 +481,7 @@
         <v>9909909909</v>
       </c>
       <c r="F2" t="str">
-        <v>Emmy86@hotmail.com</v>
+        <v>Clay_Prohaska@yahoo.com</v>
       </c>
       <c r="G2" t="str">
         <v>1990-05-16</v>

--- a/testdata/sample_employee_details_T001.xlsx
+++ b/testdata/sample_employee_details_T001.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AUIN37</v>
+        <v>AIQH57</v>
       </c>
       <c r="B2" t="str">
-        <v>Johnpaul</v>
+        <v>Heaven</v>
       </c>
       <c r="C2" t="str">
-        <v>Blanda</v>
+        <v>Macejkovic</v>
       </c>
       <c r="D2" t="str">
         <v>Male</v>
@@ -481,7 +481,7 @@
         <v>9909909909</v>
       </c>
       <c r="F2" t="str">
-        <v>Clay_Prohaska@yahoo.com</v>
+        <v>Dianne69@gmail.com</v>
       </c>
       <c r="G2" t="str">
         <v>1990-05-16</v>

--- a/testdata/sample_employee_details_T001.xlsx
+++ b/testdata/sample_employee_details_T001.xlsx
@@ -466,13 +466,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AIQH57</v>
+        <v>AUCQ80</v>
       </c>
       <c r="B2" t="str">
-        <v>Heaven</v>
+        <v>Raheem</v>
       </c>
       <c r="C2" t="str">
-        <v>Macejkovic</v>
+        <v>Senger</v>
       </c>
       <c r="D2" t="str">
         <v>Male</v>
@@ -481,7 +481,7 @@
         <v>9909909909</v>
       </c>
       <c r="F2" t="str">
-        <v>Dianne69@gmail.com</v>
+        <v>Pearl.OKeefe78@yahoo.com</v>
       </c>
       <c r="G2" t="str">
         <v>1990-05-16</v>
